--- a/data/trans_orig/P1401-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2012</t>
+          <t>Población con diagnóstico de cáncer en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,82 +747,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6243</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20154</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>18734</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>11883</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>28241</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>2,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11448</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6042</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20023</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>18734</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>11624</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>30137</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689290</t>
+          <t>689386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700319</t>
+          <t>700356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>685602</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>676896</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>690807</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1381785</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1372278</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1388636</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>685602</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>677027</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>691008</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1381785</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1370382</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1388895</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41205</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999920</t>
+          <t>1000633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014739</t>
+          <t>1014769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>999150</t>
+          <t>999009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1017021</t>
+          <t>1017363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2005716</t>
+          <t>2007798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2029451</t>
+          <t>2029073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>30840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744870</t>
+          <t>743676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754761</t>
+          <t>754701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>753006</t>
+          <t>753139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770085</t>
+          <t>770029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1502517</t>
+          <t>1503957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523025</t>
+          <t>1523240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40711</t>
+          <t>41092</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61746</t>
+          <t>60299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919485</t>
+          <t>920231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937377</t>
+          <t>937565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011190</t>
+          <t>1010809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1033379</t>
+          <t>1034446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1937894</t>
+          <t>1939341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967088</t>
+          <t>1966446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>53228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,74 +2119,74 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>71617</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>56327</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>93964</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>110782</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>89974</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>135408</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71617</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55781</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>90732</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>110782</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>90381</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>136569</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3372390</t>
+          <t>3373551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3398968</t>
+          <t>3399440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,77 +2232,77 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3483481</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3461134</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3498771</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6871095</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6846469</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6891903</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>98,41%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3483481</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3464366</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3499317</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6405</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6871095</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6845308</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6891496</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2016</t>
+          <t>Población con diagnóstico de cáncer en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>34160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662351</t>
+          <t>662933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672238</t>
+          <t>672934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646797</t>
+          <t>646400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663526</t>
+          <t>663518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1314309</t>
+          <t>1313479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1334338</t>
+          <t>1333533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37438</t>
+          <t>35506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1006637</t>
+          <t>1007378</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018620</t>
+          <t>1018624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1016682</t>
+          <t>1017493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1033516</t>
+          <t>1034258</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2027906</t>
+          <t>2029838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049857</t>
+          <t>2050898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748935</t>
+          <t>748262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757808</t>
+          <t>757782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>766045</t>
+          <t>765829</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>779884</t>
+          <t>779648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1520411</t>
+          <t>1520927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1536106</t>
+          <t>1535807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40784</t>
+          <t>42647</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28648</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56499</t>
+          <t>55392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918306</t>
+          <t>918185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931406</t>
+          <t>931681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002995</t>
+          <t>1001132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1024149</t>
+          <t>1024234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1924847</t>
+          <t>1925954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952698</t>
+          <t>1952201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40577</t>
+          <t>41430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55598</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>94528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81462</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123133</t>
+          <t>122264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3353773</t>
+          <t>3352920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373822</t>
+          <t>3374310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3453633</t>
+          <t>3450014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3488944</t>
+          <t>3489436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6815759</t>
+          <t>6816628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6857430</t>
+          <t>6856642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2023</t>
+          <t>Población con diagnóstico de cáncer en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617882</t>
+          <t>617534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628746</t>
+          <t>628630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652208</t>
+          <t>652484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663856</t>
+          <t>663938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1274594</t>
+          <t>1274313</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1290554</t>
+          <t>1290604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55359</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1160649</t>
+          <t>1161635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1182896</t>
+          <t>1183863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927156</t>
+          <t>926303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>940865</t>
+          <t>940619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2094556</t>
+          <t>2093392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2121114</t>
+          <t>2121700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36597</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677301</t>
+          <t>678211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>691786</t>
+          <t>691913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>912286</t>
+          <t>912985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>925490</t>
+          <t>925931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1594271</t>
+          <t>1594572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1615207</t>
+          <t>1615426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16361</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20965</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65163</t>
+          <t>64073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890640</t>
+          <t>891443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908611</t>
+          <t>909167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1054083</t>
+          <t>1053896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1070949</t>
+          <t>1071203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951723</t>
+          <t>1952813</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1976408</t>
+          <t>1975838</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86048</t>
+          <t>85695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62072</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>93196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>123640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170844</t>
+          <t>170753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3367410</t>
+          <t>3367763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3402239</t>
+          <t>3400496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3562756</t>
+          <t>3561826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3592950</t>
+          <t>3594330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6937636</t>
+          <t>6937727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6984036</t>
+          <t>6984840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1401-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28241</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689386</t>
+          <t>688798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700356</t>
+          <t>700397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>676896</t>
+          <t>676746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>690807</t>
+          <t>690802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1372278</t>
+          <t>1371003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1388636</t>
+          <t>1389105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1000633</t>
+          <t>1001186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014769</t>
+          <t>1014727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>999009</t>
+          <t>998070</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1017363</t>
+          <t>1017988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007798</t>
+          <t>2005985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2029073</t>
+          <t>2028761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743676</t>
+          <t>743012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754701</t>
+          <t>754666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>753139</t>
+          <t>753471</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770029</t>
+          <t>770248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503957</t>
+          <t>1501749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523240</t>
+          <t>1522683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41092</t>
+          <t>41190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>32340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60299</t>
+          <t>58972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>920231</t>
+          <t>920204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937565</t>
+          <t>937841</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010809</t>
+          <t>1010711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034446</t>
+          <t>1034647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939341</t>
+          <t>1940668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966446</t>
+          <t>1967300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>54935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93964</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>91287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135408</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3373551</t>
+          <t>3371844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3399440</t>
+          <t>3398134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3461134</t>
+          <t>3466282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3498771</t>
+          <t>3500248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6846469</t>
+          <t>6847508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6891903</t>
+          <t>6890590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>26272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>13837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662933</t>
+          <t>660630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672934</t>
+          <t>672343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646400</t>
+          <t>646567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663518</t>
+          <t>663053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1313479</t>
+          <t>1314027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1333533</t>
+          <t>1333802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35506</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007378</t>
+          <t>1007054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018624</t>
+          <t>1018651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1017493</t>
+          <t>1015168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1034258</t>
+          <t>1033435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2029838</t>
+          <t>2030563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2050898</t>
+          <t>2050847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>23844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748262</t>
+          <t>749795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757782</t>
+          <t>757822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>765829</t>
+          <t>765165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>779648</t>
+          <t>780148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1520927</t>
+          <t>1520719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1535807</t>
+          <t>1535877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>55790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918185</t>
+          <t>918860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931681</t>
+          <t>931607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1001132</t>
+          <t>1001618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1024234</t>
+          <t>1024235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1925954</t>
+          <t>1925556</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952201</t>
+          <t>1952924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41430</t>
+          <t>42386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94528</t>
+          <t>90386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122264</t>
+          <t>123352</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3352920</t>
+          <t>3351964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3374310</t>
+          <t>3373149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3450014</t>
+          <t>3454156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3489436</t>
+          <t>3491109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6816628</t>
+          <t>6815540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6856642</t>
+          <t>6855940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>624128</t>
+          <t>677957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>617534</t>
+          <t>670922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628630</t>
+          <t>682935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>659108</t>
+          <t>714821</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652484</t>
+          <t>707778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663938</t>
+          <t>720093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1283236</t>
+          <t>1392777</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1274313</t>
+          <t>1383634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1290604</t>
+          <t>1399861</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31229</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>58740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1172592</t>
+          <t>1027767</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1161635</t>
+          <t>1018040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1183863</t>
+          <t>1035301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>934746</t>
+          <t>1046042</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>926303</t>
+          <t>1037569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>940619</t>
+          <t>1052521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2107338</t>
+          <t>2073810</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2093392</t>
+          <t>2059956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2121700</t>
+          <t>2083453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957051</t>
+          <t>1069778</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957051</t>
+          <t>1069778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957051</t>
+          <t>1069778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149915</t>
+          <t>2118696</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149915</t>
+          <t>2118696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149915</t>
+          <t>2118696</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,102 +5307,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18594</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>27501</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>18969</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>39733</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10914</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4756</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17702</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>25043</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>15442</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>36296</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5420,102 +5420,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>686052</t>
+          <t>782698</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>678211</t>
+          <t>772923</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>691913</t>
+          <t>788328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>796763</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>790169</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>801077</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1579461</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1567229</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1587993</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>98,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>919773</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>912985</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>925931</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1605825</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1594572</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1615426</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>700181</t>
+          <t>798199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>700181</t>
+          <t>798199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>700181</t>
+          <t>798199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>930687</t>
+          <t>808763</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930687</t>
+          <t>808763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>930687</t>
+          <t>808763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1630868</t>
+          <t>1606962</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1630868</t>
+          <t>1606962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1630868</t>
+          <t>1606962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51622</t>
+          <t>56284</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>44689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>901808</t>
+          <t>962076</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891443</t>
+          <t>952658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909167</t>
+          <t>970168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1063456</t>
+          <t>1086453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1053896</t>
+          <t>1077412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1071203</t>
+          <t>1093542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1965264</t>
+          <t>2048529</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952813</t>
+          <t>2035906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975838</t>
+          <t>2060124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924972</t>
+          <t>987179</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924972</t>
+          <t>987179</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924972</t>
+          <t>987179</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2016886</t>
+          <t>2104813</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2016886</t>
+          <t>2104813</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2016886</t>
+          <t>2104813</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85695</t>
+          <t>90426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60692</t>
+          <t>71138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93196</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123640</t>
+          <t>140385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170753</t>
+          <t>181701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3384581</t>
+          <t>3450497</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3367763</t>
+          <t>3434578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3400496</t>
+          <t>3466743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3577082</t>
+          <t>3644079</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3561826</t>
+          <t>3630709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3594330</t>
+          <t>3657759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6961663</t>
+          <t>7094576</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6937727</t>
+          <t>7072200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6984840</t>
+          <t>7113516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3453458</t>
+          <t>3525004</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655022</t>
+          <t>3728897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7108480</t>
+          <t>7253901</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
